--- a/data/credits.xlsx
+++ b/data/credits.xlsx
@@ -399,17 +399,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I44"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="6.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="50.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -486,7 +475,7 @@
         <v>https://sanferminband.bandcamp.com/album/arms</v>
       </c>
       <c r="F3" t="str">
-        <v>https://open.spotify.com/track/4cQpA3lSvchIKnmo1fzEAL</v>
+        <v>https://open.spotify.com/album/5grHCZZ9MudkWc1yFq8RQC</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -863,7 +852,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>https://open.spotify.com/track/67djP6VPqGDjG5jJgBEuQb</v>
+        <v>https://open.spotify.com/album/7weMOuQtaLZ5IM1FFpSv8v</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1124,7 +1113,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>https://open.spotify.com/track/45IryAtCyBE0zAdYe77Lll</v>
+        <v>https://open.spotify.com/album/5YCkSdO04tHwrurgYzN09v</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1211,7 +1200,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>https://open.spotify.com/track/0MBupnLliwp226j5RSaPt0</v>
+        <v>https://open.spotify.com/album/4DRVBIISdoxJAb7Syh3gSt</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1530,7 +1519,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>https://open.spotify.com/track/2um4ISitgBDdMSZaiPyaIb</v>
+        <v>https://open.spotify.com/album/4ek7xLvUQ1XJW5iVGjRg6l</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1697,12 +1686,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D268"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data/credits.xlsx
+++ b/data/credits.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Releases" sheetId="1" r:id="rId1"/>
     <sheet name="Tracks" sheetId="2" r:id="rId2"/>
+    <sheet name="Artists" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:N45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,9 +424,24 @@
         <v>youtube</v>
       </c>
       <c r="H1" t="str">
+        <v>website</v>
+      </c>
+      <c r="I1" t="str">
+        <v>instagram</v>
+      </c>
+      <c r="J1" t="str">
+        <v>tiktok</v>
+      </c>
+      <c r="K1" t="str">
+        <v>artworkUrl</v>
+      </c>
+      <c r="L1" t="str">
+        <v>bandcampEmbedUrl</v>
+      </c>
+      <c r="M1" t="str">
         <v>description</v>
       </c>
-      <c r="I1" t="str">
+      <c r="N1" t="str">
         <v>createdAt</v>
       </c>
     </row>
@@ -452,9 +468,24 @@
         <v>https://www.youtube.com/watch?v=WTQtj7H492M</v>
       </c>
       <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I2" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2731f1e891905514beced17a8c0</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2">
         <v>1789227594960</v>
       </c>
     </row>
@@ -481,9 +512,24 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I3" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273d141a813960d6a7b6376bd11</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3">
         <v>20240023</v>
       </c>
     </row>
@@ -504,15 +550,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/album/a-trip-to-the-moon</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/3zIfzm0zYZDQs1XQvTSHOn?si=NkKpaQmFRF6u7amf3KXHxg</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I4" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2730f05e009584a6bf05aec6a24</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4">
         <v>20240008</v>
       </c>
     </row>
@@ -541,7 +602,22 @@
       <c r="H5" t="str">
         <v/>
       </c>
-      <c r="I5">
+      <c r="I5" t="str">
+        <v>https://instagram.com/halliespoormusic</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27377b8a765154250377d3ded3e</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5">
         <v>20230019</v>
       </c>
     </row>
@@ -570,7 +646,22 @@
       <c r="H6" t="str">
         <v/>
       </c>
-      <c r="I6">
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>https://i.scdn.co/image/ab6765630000ba8a20f43cab698be43c63d498e8</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6">
         <v>20220037</v>
       </c>
     </row>
@@ -599,7 +690,22 @@
       <c r="H7" t="str">
         <v/>
       </c>
-      <c r="I7">
+      <c r="I7" t="str">
+        <v>https://instagram.com/stereotrashs</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2738ead0b92ddd3054b969a2d5c</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7">
         <v>20220033</v>
       </c>
     </row>
@@ -626,9 +732,24 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I8" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273ad78cde3fc07afe308cf8461</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8">
         <v>20220029</v>
       </c>
     </row>
@@ -657,7 +778,22 @@
       <c r="H9" t="str">
         <v/>
       </c>
-      <c r="I9">
+      <c r="I9" t="str">
+        <v>https://instagram.com/majaeshin</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273991e5ca63a2eda83b3b27e4b</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9">
         <v>20220020</v>
       </c>
     </row>
@@ -678,15 +814,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/track/bedford</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/0gPUN2e9YnooniaMYJm1qP?si=JLHeIF12SY2EondRnZiMmQ</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I10" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2738858d5833b32c4cd62444670</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10">
         <v>20220011</v>
       </c>
     </row>
@@ -707,15 +858,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/album/a-new-kind-of-love</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/1lh56A3GCbVdwUNZQAFs6r?si=NIyTzBFoSkG_efrgx2mhJQ</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I11" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273d5082610734636a4df70767b</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11">
         <v>20220006</v>
       </c>
     </row>
@@ -724,7 +890,7 @@
         <v>fuck-la-i-love-la-deluxe-edition</v>
       </c>
       <c r="B12" t="str">
-        <v>Fuck LA / I Love LA (deluxe edition)</v>
+        <v>Fuck LA / I Love LA</v>
       </c>
       <c r="C12" t="str">
         <v>Behaviorist</v>
@@ -742,9 +908,24 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12">
+        <v>https://behavioristmusic.com</v>
+      </c>
+      <c r="I12" t="str">
+        <v>https://instagram.com/behavioristmusic</v>
+      </c>
+      <c r="J12" t="str">
+        <v>https://www.tiktok.com/@behavioristmusic</v>
+      </c>
+      <c r="K12" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273ad17f606fbae71d0d8c83746</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12">
         <v>20220002</v>
       </c>
     </row>
@@ -765,7 +946,7 @@
         <v>https://wildpink.bandcamp.com/album/a-billion-little-lights</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/0fHchXs9fUUcnzXpmzdAr1?si=9a82fd57a7154fc1</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -773,7 +954,22 @@
       <c r="H13" t="str">
         <v/>
       </c>
-      <c r="I13">
+      <c r="I13" t="str">
+        <v>https://instagram.com/wildpinknyc</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27319f449340448495c26caaf08</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13">
         <v>20210040</v>
       </c>
     </row>
@@ -794,7 +990,7 @@
         <v>https://wildpink.bandcamp.com/album/3-songs</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/46YarlzhDQ9CvbDKovOxkJ?si=5tnMH0lnQwa9bk_bNgBwAA</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -802,7 +998,22 @@
       <c r="H14" t="str">
         <v/>
       </c>
-      <c r="I14">
+      <c r="I14" t="str">
+        <v>https://instagram.com/wildpinknyc</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273b8129cc197fc2d04654ff06d</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14">
         <v>20210039</v>
       </c>
     </row>
@@ -831,7 +1042,22 @@
       <c r="H15" t="str">
         <v/>
       </c>
-      <c r="I15">
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>https://i.scdn.co/image/ab6761610000e5eb9c31029154ab375ef6e93adf</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15">
         <v>20210038</v>
       </c>
     </row>
@@ -860,7 +1086,22 @@
       <c r="H16" t="str">
         <v/>
       </c>
-      <c r="I16">
+      <c r="I16" t="str">
+        <v>https://instagram.com/tallheights</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27315dcbf4fc1882e725c228aa3</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16">
         <v>20210034</v>
       </c>
     </row>
@@ -889,7 +1130,22 @@
       <c r="H17" t="str">
         <v/>
       </c>
-      <c r="I17">
+      <c r="I17" t="str">
+        <v>https://instagram.com/jorge_elbrecht</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17">
         <v>20210021</v>
       </c>
     </row>
@@ -910,15 +1166,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/album/varsovia</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/7mbFgnYdXemCc2cptaDMEK?si=b_Ae4dWaQR6p-Bvsmue8Pg</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I18" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273da81305f6752504bd631d144</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18">
         <v>20210014</v>
       </c>
     </row>
@@ -939,15 +1210,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/track/asphalt-homeland</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/1HaBESCS3hkqIJ4Da2vanc?si=vkRaLA3kQoGEDgE1Z86ajA</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>https://www.youtube.com/channel/UCteCBPlznRp8U7Z6MDBQEkA</v>
       </c>
       <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I19" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2737a95f9a7ea97e1fa052ef512</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19">
         <v>20210010</v>
       </c>
     </row>
@@ -976,7 +1262,22 @@
       <c r="H20" t="str">
         <v/>
       </c>
-      <c r="I20">
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273d5ab4a58176f8d94370051a0</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20">
         <v>20210004</v>
       </c>
     </row>
@@ -997,15 +1298,30 @@
         <v>https://behaviorist.bandcamp.com/album/cassandra-deluxe-edition</v>
       </c>
       <c r="F21" t="str">
-        <v>https://open.spotify.com/album/4aaq7xxsgMU1hWCZ7K7DE9</v>
+        <v>https://open.spotify.com/album/1qVFoxSTlYlJAjT8yMcRgz</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21">
+        <v>https://behavioristmusic.com</v>
+      </c>
+      <c r="I21" t="str">
+        <v>https://instagram.com/behavioristmusic</v>
+      </c>
+      <c r="J21" t="str">
+        <v>https://www.tiktok.com/@behavioristmusic</v>
+      </c>
+      <c r="K21" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273a42c5221de598165452b496b</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21">
         <v>20210001</v>
       </c>
     </row>
@@ -1034,7 +1350,22 @@
       <c r="H22" t="str">
         <v/>
       </c>
-      <c r="I22">
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2737430089cc034518597eff1b3</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22">
         <v>20200022</v>
       </c>
     </row>
@@ -1061,9 +1392,24 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I23" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>https://bandcamp.com/EmbeddedPlayer/album=3710202166/size=large/bgcol=ffffff/linkcol=0687f5/tracklist=false/transparent=true/</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23">
         <v>20200013</v>
       </c>
     </row>
@@ -1084,15 +1430,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/album/an-ode-to-escapism</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/3X4VjrndF9GROzpR6r9UK9?si=yX7sKVsJT2-k2jside9oSw</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I24" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27352edce5f06f82ef03c9e8e1c</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24">
         <v>20200009</v>
       </c>
     </row>
@@ -1121,7 +1482,22 @@
       <c r="H25" t="str">
         <v/>
       </c>
-      <c r="I25">
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273aa809935b7d31c35d9c8f37c</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25">
         <v>20200005</v>
       </c>
     </row>
@@ -1150,7 +1526,22 @@
       <c r="H26" t="str">
         <v/>
       </c>
-      <c r="I26">
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26">
         <v>20190041</v>
       </c>
     </row>
@@ -1179,7 +1570,22 @@
       <c r="H27" t="str">
         <v/>
       </c>
-      <c r="I27">
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27">
         <v>20190036</v>
       </c>
     </row>
@@ -1208,7 +1614,22 @@
       <c r="H28" t="str">
         <v/>
       </c>
-      <c r="I28">
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273a71f163217d379161421aff6</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28">
         <v>20190031</v>
       </c>
     </row>
@@ -1229,7 +1650,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>https://open.spotify.com/track/1oGMvha55cjNWAWpY7uEl5?si=451e33135aae46a9</v>
       </c>
       <c r="G29" t="str">
         <v>https://youtu.be/CauZkU4HJjE</v>
@@ -1237,7 +1658,22 @@
       <c r="H29" t="str">
         <v/>
       </c>
-      <c r="I29">
+      <c r="I29" t="str">
+        <v>https://instagram.com/scamavenue</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273422115ffb62247794ffb980f</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29">
         <v>20190030</v>
       </c>
     </row>
@@ -1264,9 +1700,24 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I30" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273274e4163e27a660e0b8ac93b</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30">
         <v>20190028</v>
       </c>
     </row>
@@ -1293,9 +1744,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I31" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2738a95b2753aa679638c4e35bc</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31">
         <v>20190026</v>
       </c>
     </row>
@@ -1316,15 +1782,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/album/a-song-for-paul-2</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/0w6knr7boQarN35qErXXeu?si=oiQW598lQQiG-D85ZgsANQ</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I32" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27305ca63c4ea9702eb9dfa85a7</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32">
         <v>20190007</v>
       </c>
     </row>
@@ -1351,9 +1832,24 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33">
+        <v>https://behavioristmusic.com</v>
+      </c>
+      <c r="I33" t="str">
+        <v>https://instagram.com/behavioristmusic</v>
+      </c>
+      <c r="J33" t="str">
+        <v>https://www.tiktok.com/@behavioristmusic</v>
+      </c>
+      <c r="K33" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b2739ca9e4a8561cad454564d68f</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33">
         <v>20190000</v>
       </c>
     </row>
@@ -1374,7 +1870,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/7p8yetiDX9hpBsucJ1tTIr?si=b60dbd9fdffa4c2e</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1382,7 +1878,22 @@
       <c r="H34" t="str">
         <v/>
       </c>
-      <c r="I34">
+      <c r="I34" t="str">
+        <v>https://instagram.com/tallheights</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27366f76fef861482c6e7215e61</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34">
         <v>20180035</v>
       </c>
     </row>
@@ -1411,7 +1922,22 @@
       <c r="H35" t="str">
         <v/>
       </c>
-      <c r="I35">
+      <c r="I35" t="str">
+        <v>https://instagram.com/stereotrashs</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>uploads/1789374994739-f38ae8fd.jpg</v>
+      </c>
+      <c r="L35" t="str">
+        <v>https://bandcamp.com/EmbeddedPlayer/album=4142148916/size=large/bgcol=ffffff/linkcol=0687f5/tracklist=false/transparent=true/</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Combining anthemic choruses with a pop sensibility,</v>
+      </c>
+      <c r="N35">
         <v>20180032</v>
       </c>
     </row>
@@ -1438,9 +1964,24 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I36" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273891ecc1b2ea482292d8056f5</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36">
         <v>20170024</v>
       </c>
     </row>
@@ -1469,7 +2010,22 @@
       <c r="H37" t="str">
         <v/>
       </c>
-      <c r="I37">
+      <c r="I37" t="str">
+        <v>https://instagram.com/greatcaesarband</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27368eb59dc490bced504de0f31</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37">
         <v>20160016</v>
       </c>
     </row>
@@ -1490,15 +2046,30 @@
         <v>https://ghostfunkorchestra.bandcamp.com/album/night-walker-death-waltz</v>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/0SAqFTj0OmnFJy1ru1s6g0?si=tEzMwKGTQvutP2gywJ1drg</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="I38" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273acef63e0da0e41968af47981</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38">
         <v>20160012</v>
       </c>
     </row>
@@ -1527,7 +2098,22 @@
       <c r="H39" t="str">
         <v/>
       </c>
-      <c r="I39">
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273c0eedc41ffad321f38f51b4f</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39">
         <v>20160003</v>
       </c>
     </row>
@@ -1554,9 +2140,24 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I40" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273092ec959e1604be024279ec9</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40">
         <v>20150025</v>
       </c>
     </row>
@@ -1577,7 +2178,7 @@
         <v>https://greatcaesar.bandcamp.com/track/sharks</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>https://open.spotify.com/album/6Xdd609ic8Claf4fHzFzk6?si=5f5ed487947341b2</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1585,7 +2186,22 @@
       <c r="H41" t="str">
         <v/>
       </c>
-      <c r="I41">
+      <c r="I41" t="str">
+        <v>https://instagram.com/greatcaesarband</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273799bcc84708ef4c58121d436</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41">
         <v>20150018</v>
       </c>
     </row>
@@ -1614,7 +2230,22 @@
       <c r="H42" t="str">
         <v/>
       </c>
-      <c r="I42">
+      <c r="I42" t="str">
+        <v>https://instagram.com/greatcaesarband</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273f6eefabd474b1ed8bc7805f4</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42">
         <v>20140015</v>
       </c>
     </row>
@@ -1641,9 +2272,24 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="I43" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273d285503358c3be6e2067e74b</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43">
         <v>20130027</v>
       </c>
     </row>
@@ -1672,20 +2318,79 @@
       <c r="H44" t="str">
         <v/>
       </c>
-      <c r="I44">
+      <c r="I44" t="str">
+        <v>https://instagram.com/greatcaesarband</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b27382348d9ddaba8814ad66b8a6</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44">
         <v>20120017</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>extra-nice</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Extra Nice</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Extra Nice</v>
+      </c>
+      <c r="D45">
+        <v>2026</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>https://open.spotify.com/album/52mUAU7iTwJPGa4pphN6dL</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>https://instagram.com/extranicemusic</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>https://i.scdn.co/image/ab67616d0000b273460f10ff87882eb799f3ef52</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>The debut of this fantastic duo project with Romi Hanoch.</v>
+      </c>
+      <c r="N45">
+        <v>1789371418942</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D272"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1857,10 +2562,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>arms</v>
+        <v>v-interesting-theme</v>
       </c>
       <c r="B13" t="str">
-        <v>Weird Environment</v>
+        <v>V Interesting (Theme)</v>
       </c>
       <c r="C13" t="str">
         <v>saxophone</v>
@@ -1871,13 +2576,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B14" t="str">
-        <v>Didn't Want You To</v>
+        <v>Intro</v>
       </c>
       <c r="C14" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D14" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1885,13 +2590,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B15" t="str">
-        <v>Can't Unsee It</v>
+        <v>Alan</v>
       </c>
       <c r="C15" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D15" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1899,13 +2604,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B16" t="str">
-        <v>Arms</v>
+        <v>Rock Show</v>
       </c>
       <c r="C16" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D16" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1913,13 +2618,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B17" t="str">
-        <v>Makes Me Want You</v>
+        <v>People Talking In Conversation</v>
       </c>
       <c r="C17" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D17" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1927,13 +2632,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B18" t="str">
-        <v>My Love is a Loneliness</v>
+        <v>Jesus Has a Big Dick</v>
       </c>
       <c r="C18" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D18" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1941,13 +2646,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B19" t="str">
-        <v>Useful Lies</v>
+        <v>Hastag</v>
       </c>
       <c r="C19" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D19" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1955,13 +2660,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B20" t="str">
-        <v>Wasting on Me</v>
+        <v>Parking Lot</v>
       </c>
       <c r="C20" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D20" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1969,13 +2674,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>arms</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B21" t="str">
-        <v>You Owe Me</v>
+        <v>Love</v>
       </c>
       <c r="C21" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D21" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1983,13 +2688,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B22" t="str">
-        <v>Opening</v>
+        <v>How 2 Count</v>
       </c>
       <c r="C22" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D22" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -1997,13 +2702,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B23" t="str">
-        <v>Eyes of Love</v>
+        <v>The Hits Keep Coming</v>
       </c>
       <c r="C23" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D23" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2011,13 +2716,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B24" t="str">
-        <v>Where To?</v>
+        <v>Upppder East Side</v>
       </c>
       <c r="C24" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D24" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2025,13 +2730,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B25" t="str">
-        <v>To The Moon!</v>
+        <v>Wasted Intro</v>
       </c>
       <c r="C25" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D25" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2039,13 +2744,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B26" t="str">
-        <v>Achluo</v>
+        <v>Wasted</v>
       </c>
       <c r="C26" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D26" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2053,13 +2758,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>raw-masters-wav-exe</v>
       </c>
       <c r="B27" t="str">
-        <v>Nova</v>
+        <v>Really Good Secret Hidden Track (remember to not post)</v>
       </c>
       <c r="C27" t="str">
-        <v>saxophone</v>
+        <v>drums, vocals, writing</v>
       </c>
       <c r="D27" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2067,10 +2772,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>your-ghost</v>
       </c>
       <c r="B28" t="str">
-        <v>Helios</v>
+        <v>Tired of Loving You</v>
       </c>
       <c r="C28" t="str">
         <v>saxophone</v>
@@ -2081,10 +2786,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>your-ghost</v>
       </c>
       <c r="B29" t="str">
-        <v>Into The Abyss</v>
+        <v>Someone You Call Baby</v>
       </c>
       <c r="C29" t="str">
         <v>saxophone</v>
@@ -2095,10 +2800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>your-ghost</v>
       </c>
       <c r="B30" t="str">
-        <v>Again</v>
+        <v>Your Ghost</v>
       </c>
       <c r="C30" t="str">
         <v>saxophone</v>
@@ -2109,13 +2814,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>dangerous-energy-ep</v>
       </c>
       <c r="B31" t="str">
-        <v>A Solar Wind</v>
+        <v>Dangerous Energy</v>
       </c>
       <c r="C31" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
       </c>
       <c r="D31" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2123,13 +2828,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>dangerous-energy-ep</v>
       </c>
       <c r="B32" t="str">
-        <v>Space Walk</v>
+        <v>Monday Song</v>
       </c>
       <c r="C32" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
       </c>
       <c r="D32" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2137,13 +2842,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>dangerous-energy-ep</v>
       </c>
       <c r="B33" t="str">
-        <v>Casadastra</v>
+        <v>Here</v>
       </c>
       <c r="C33" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
       </c>
       <c r="D33" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2151,13 +2856,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>dangerous-energy-ep</v>
       </c>
       <c r="B34" t="str">
-        <v>A Rare View</v>
+        <v>Not Your Friend</v>
       </c>
       <c r="C34" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
       </c>
       <c r="D34" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2165,10 +2870,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>flyin-overhead-single</v>
       </c>
       <c r="B35" t="str">
-        <v>Totality</v>
+        <v>Flyin' Overhead (single)</v>
       </c>
       <c r="C35" t="str">
         <v>saxophone</v>
@@ -2179,13 +2884,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>a-trip-to-the-moon</v>
+        <v>unknown-caller</v>
       </c>
       <c r="B36" t="str">
-        <v>Infinite Dark</v>
+        <v>Folded Up</v>
       </c>
       <c r="C36" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D36" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2193,13 +2898,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>heart-like-thunder</v>
+        <v>unknown-caller</v>
       </c>
       <c r="B37" t="str">
-        <v>County Road 458</v>
+        <v>How to Be Alone</v>
       </c>
       <c r="C37" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D37" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2207,13 +2912,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>heart-like-thunder</v>
+        <v>unknown-caller</v>
       </c>
       <c r="B38" t="str">
-        <v>Goodbye</v>
+        <v>June 20th, 1943</v>
       </c>
       <c r="C38" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D38" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2221,13 +2926,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>heart-like-thunder</v>
+        <v>xito</v>
       </c>
       <c r="B39" t="str">
-        <v>Julia</v>
+        <v>Welcome to the Boogie</v>
       </c>
       <c r="C39" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>producing, arranging</v>
       </c>
       <c r="D39" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2235,13 +2940,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>heart-like-thunder</v>
+        <v>xito</v>
       </c>
       <c r="B40" t="str">
-        <v>Diamond Ring</v>
+        <v>Salvation</v>
       </c>
       <c r="C40" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>producing, arranging</v>
       </c>
       <c r="D40" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2249,13 +2954,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>heart-like-thunder</v>
+        <v>xito</v>
       </c>
       <c r="B41" t="str">
-        <v>Heart Like Thunder</v>
+        <v>En Guayubin No Llueve</v>
       </c>
       <c r="C41" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>producing, arranging</v>
       </c>
       <c r="D41" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2263,13 +2968,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>heart-like-thunder</v>
+        <v>xito</v>
       </c>
       <c r="B42" t="str">
-        <v>Geraldine</v>
+        <v>Sugar</v>
       </c>
       <c r="C42" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>producing, arranging</v>
       </c>
       <c r="D42" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2277,13 +2982,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>heart-like-thunder</v>
+        <v>xito</v>
       </c>
       <c r="B43" t="str">
-        <v>Shenandoah</v>
+        <v>Tu Si Puedes</v>
       </c>
       <c r="C43" t="str">
-        <v>producing, arranging, flute, clarinet, saxophone, engineering</v>
+        <v>producing, arranging, saxophone</v>
       </c>
       <c r="D43" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2291,10 +2996,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>v-interesting-theme</v>
+        <v>every-feeling-i-ve-ever-felt</v>
       </c>
       <c r="B44" t="str">
-        <v>V Interesting (Theme)</v>
+        <v>Every Feeling I've Ever Felt</v>
       </c>
       <c r="C44" t="str">
         <v>saxophone</v>
@@ -2305,13 +3010,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>still-here</v>
       </c>
       <c r="B45" t="str">
-        <v>Intro</v>
+        <v>I Knew It Was You</v>
       </c>
       <c r="C45" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D45" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2319,13 +3024,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>rain-on-havana</v>
       </c>
       <c r="B46" t="str">
-        <v>Alan</v>
+        <v>Rain on Havana</v>
       </c>
       <c r="C46" t="str">
-        <v>drums, vocals, writing</v>
+        <v>bass</v>
       </c>
       <c r="D46" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2333,13 +3038,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>don-t-forget-single</v>
       </c>
       <c r="B47" t="str">
-        <v>Rock Show</v>
+        <v>Don't Forget (single)</v>
       </c>
       <c r="C47" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D47" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2347,13 +3052,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B48" t="str">
-        <v>People Talking In Conversation</v>
+        <v>The Cormorant</v>
       </c>
       <c r="C48" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D48" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2361,13 +3066,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B49" t="str">
-        <v>Jesus Has a Big Dick</v>
+        <v>Cerulean Gardens</v>
       </c>
       <c r="C49" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D49" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2375,13 +3080,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B50" t="str">
-        <v>Hastag</v>
+        <v>Hickman Creek</v>
       </c>
       <c r="C50" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D50" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2389,13 +3094,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B51" t="str">
-        <v>Parking Lot</v>
+        <v>The Hunger</v>
       </c>
       <c r="C51" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D51" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2403,13 +3108,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B52" t="str">
-        <v>Love</v>
+        <v>Summer by the Void</v>
       </c>
       <c r="C52" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D52" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2417,13 +3122,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B53" t="str">
-        <v>How 2 Count</v>
+        <v>Saints</v>
       </c>
       <c r="C53" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D53" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2431,13 +3136,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B54" t="str">
-        <v>The Hits Keep Coming</v>
+        <v>The Living</v>
       </c>
       <c r="C54" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D54" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2445,13 +3150,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B55" t="str">
-        <v>Upppder East Side</v>
+        <v>The Myth</v>
       </c>
       <c r="C55" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D55" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2459,13 +3164,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B56" t="str">
-        <v>Wasted Intro</v>
+        <v>Swamp Song</v>
       </c>
       <c r="C56" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D56" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2473,13 +3178,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B57" t="str">
-        <v>Wasted</v>
+        <v>Westfjords</v>
       </c>
       <c r="C57" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D57" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2487,13 +3192,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>raw-masters-wav-exe</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B58" t="str">
-        <v>Really Good Secret Hidden Track (remember to not post)</v>
+        <v>Do Less</v>
       </c>
       <c r="C58" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone</v>
       </c>
       <c r="D58" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2501,10 +3206,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>your-ghost</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B59" t="str">
-        <v>Tired of Loving You</v>
+        <v>Little Star</v>
       </c>
       <c r="C59" t="str">
         <v>saxophone</v>
@@ -2515,10 +3220,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>your-ghost</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B60" t="str">
-        <v>Someone You Call Baby</v>
+        <v>Berkley Bridge</v>
       </c>
       <c r="C60" t="str">
         <v>saxophone</v>
@@ -2529,10 +3234,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>your-ghost</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B61" t="str">
-        <v>Your Ghost</v>
+        <v>Freedom (Yeah Yeah!)</v>
       </c>
       <c r="C61" t="str">
         <v>saxophone</v>
@@ -2543,13 +3248,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>bugs</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B62" t="str">
-        <v>Callous</v>
+        <v>Waterworld</v>
       </c>
       <c r="C62" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D62" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2557,13 +3262,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bugs</v>
+        <v>the-cormorant-i-ii</v>
       </c>
       <c r="B63" t="str">
-        <v>Stay</v>
+        <v>Tunnel Mt.</v>
       </c>
       <c r="C63" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D63" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2571,13 +3276,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B64" t="str">
-        <v>Scatter</v>
+        <v>The Woods - Live</v>
       </c>
       <c r="C64" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D64" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2585,13 +3290,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B65" t="str">
-        <v>Here to Stay</v>
+        <v>Bride - Live</v>
       </c>
       <c r="C65" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D65" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2599,13 +3304,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B66" t="str">
-        <v>Grow Old</v>
+        <v>Emily - Live</v>
       </c>
       <c r="C66" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D66" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2613,13 +3318,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B67" t="str">
-        <v>Inimitable</v>
+        <v>Open - Live</v>
       </c>
       <c r="C67" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D67" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2627,13 +3332,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B68" t="str">
-        <v>Intention</v>
+        <v>Better Company - Live</v>
       </c>
       <c r="C68" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D68" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2641,13 +3346,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B69" t="str">
-        <v>Lighter Shouldered</v>
+        <v>No Promises - Live</v>
       </c>
       <c r="C69" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D69" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2655,13 +3360,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B70" t="str">
-        <v>Typical</v>
+        <v>Methuselah - Live</v>
       </c>
       <c r="C70" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D70" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2669,13 +3374,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>bugs</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B71" t="str">
-        <v>Lilac</v>
+        <v>At Sea - Live</v>
       </c>
       <c r="C71" t="str">
-        <v>saxophone, arranging, producing, engineering, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D71" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2683,10 +3388,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>bedford-single</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B72" t="str">
-        <v>Bedford (Single)</v>
+        <v>Ladies Mary - Live</v>
       </c>
       <c r="C72" t="str">
         <v>saxophone</v>
@@ -2697,13 +3402,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B73" t="str">
-        <v>Introduction</v>
+        <v>Oceanica - Live</v>
       </c>
       <c r="C73" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D73" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2711,13 +3416,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B74" t="str">
-        <v>Your Man's No Good</v>
+        <v>Dead - Live</v>
       </c>
       <c r="C74" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D74" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2725,10 +3430,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B75" t="str">
-        <v>Scatter</v>
+        <v>Astronaut - Live</v>
       </c>
       <c r="C75" t="str">
         <v>saxophone</v>
@@ -2739,13 +3444,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B76" t="str">
-        <v>Prism</v>
+        <v>Cairo - Live</v>
       </c>
       <c r="C76" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D76" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2753,13 +3458,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B77" t="str">
-        <v>Quiet Places</v>
+        <v>Oh Darling - Live</v>
       </c>
       <c r="C77" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D77" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2767,13 +3472,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B78" t="str">
-        <v>A New Kind Of Love (pt. 1)</v>
+        <v>Asleep on the Train - Live</v>
       </c>
       <c r="C78" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D78" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2781,10 +3486,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B79" t="str">
-        <v>Why?</v>
+        <v>Parasites - Live</v>
       </c>
       <c r="C79" t="str">
         <v>saxophone</v>
@@ -2795,10 +3500,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B80" t="str">
-        <v>Blockhead</v>
+        <v>Sonsick - Live</v>
       </c>
       <c r="C80" t="str">
         <v>saxophone</v>
@@ -2809,13 +3514,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B81" t="str">
-        <v>A Song For Pearl</v>
+        <v>Belong - Live</v>
       </c>
       <c r="C81" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D81" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2823,10 +3528,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B82" t="str">
-        <v>Bluebell</v>
+        <v>Palisades/Storm - Live</v>
       </c>
       <c r="C82" t="str">
         <v>saxophone</v>
@@ -2837,13 +3542,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B83" t="str">
-        <v>Rooted</v>
+        <v>Happiness Will Ruin This Place - Live</v>
       </c>
       <c r="C83" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging</v>
       </c>
       <c r="D83" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2851,10 +3556,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>a-new-kind-of-love</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B84" t="str">
-        <v>A New Kind Of Love (pt. 2)</v>
+        <v>Renaissance - Live</v>
       </c>
       <c r="C84" t="str">
         <v>saxophone</v>
@@ -2865,13 +3570,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>fuck-la-i-love-la-deluxe-edition</v>
+        <v>live-at-the-fillmore</v>
       </c>
       <c r="B85" t="str">
-        <v>Fuck LA</v>
+        <v>Jackrabbit - Live</v>
       </c>
       <c r="C85" t="str">
-        <v>saxophone, vocals, writing, arranging, producing, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D85" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2879,13 +3584,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fuck-la-i-love-la-deluxe-edition</v>
+        <v>belong</v>
       </c>
       <c r="B86" t="str">
-        <v>I Love LA</v>
+        <v>Open</v>
       </c>
       <c r="C86" t="str">
-        <v>saxophone, vocals, writing, arranging, producing, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D86" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -2893,10 +3598,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B87" t="str">
-        <v>The Wind Was Like A Train</v>
+        <v>Bride</v>
       </c>
       <c r="C87" t="str">
         <v>saxophone</v>
@@ -2907,10 +3612,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B88" t="str">
-        <v>Bigger Than Christmas</v>
+        <v>Oceanica</v>
       </c>
       <c r="C88" t="str">
         <v>saxophone</v>
@@ -2921,10 +3626,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B89" t="str">
-        <v>The Shining But Tropical</v>
+        <v>August</v>
       </c>
       <c r="C89" t="str">
         <v>saxophone</v>
@@ -2935,10 +3640,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B90" t="str">
-        <v>Amalfi</v>
+        <v>Better Company</v>
       </c>
       <c r="C90" t="str">
         <v>saxophone</v>
@@ -2949,10 +3654,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B91" t="str">
-        <v>Oversharers Anonymous</v>
+        <v>No Promises</v>
       </c>
       <c r="C91" t="str">
         <v>saxophone</v>
@@ -2963,10 +3668,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B92" t="str">
-        <v>You Can Have It Back</v>
+        <v>Belong</v>
       </c>
       <c r="C92" t="str">
         <v>saxophone</v>
@@ -2977,10 +3682,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B93" t="str">
-        <v>Family Friends</v>
+        <v>Bones</v>
       </c>
       <c r="C93" t="str">
         <v>saxophone</v>
@@ -2991,10 +3696,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B94" t="str">
-        <v>Track Mud</v>
+        <v>Dead</v>
       </c>
       <c r="C94" t="str">
         <v>saxophone</v>
@@ -3005,10 +3710,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B95" t="str">
-        <v>Pacific City</v>
+        <v>Perfume</v>
       </c>
       <c r="C95" t="str">
         <v>saxophone</v>
@@ -3019,10 +3724,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>a-billion-little-lights</v>
+        <v>belong</v>
       </c>
       <c r="B96" t="str">
-        <v>Die Outside</v>
+        <v>Cairo</v>
       </c>
       <c r="C96" t="str">
         <v>saxophone</v>
@@ -3033,10 +3738,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>3-songs</v>
+        <v>belong</v>
       </c>
       <c r="B97" t="str">
-        <v>Ohio (feat. Samia)</v>
+        <v>Palisades/Storm</v>
       </c>
       <c r="C97" t="str">
         <v>saxophone</v>
@@ -3047,10 +3752,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>3-songs</v>
+        <v>belong</v>
       </c>
       <c r="B98" t="str">
-        <v>Leferever</v>
+        <v>Happiness Will Ruin This Place</v>
       </c>
       <c r="C98" t="str">
         <v>saxophone</v>
@@ -3061,10 +3766,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>3-songs</v>
+        <v>where-do-you-go-single</v>
       </c>
       <c r="B99" t="str">
-        <v>A Scene From The Eau Gallie Causeway</v>
+        <v>Where Do You Go (Single)</v>
       </c>
       <c r="C99" t="str">
         <v>saxophone</v>
@@ -3075,13 +3780,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>dangerous-energy-ep</v>
+        <v>san-fermin</v>
       </c>
       <c r="B100" t="str">
-        <v>Dangerous Energy</v>
+        <v>Renaissance!</v>
       </c>
       <c r="C100" t="str">
-        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D100" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3089,13 +3794,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>dangerous-energy-ep</v>
+        <v>san-fermin</v>
       </c>
       <c r="B101" t="str">
-        <v>Monday Song</v>
+        <v>Crueler Kind</v>
       </c>
       <c r="C101" t="str">
-        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D101" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3103,13 +3808,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>dangerous-energy-ep</v>
+        <v>san-fermin</v>
       </c>
       <c r="B102" t="str">
-        <v>Here</v>
+        <v>Lament For V.G.</v>
       </c>
       <c r="C102" t="str">
-        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D102" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3117,13 +3822,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>dangerous-energy-ep</v>
+        <v>san-fermin</v>
       </c>
       <c r="B103" t="str">
-        <v>Not Your Friend</v>
+        <v>Casanova</v>
       </c>
       <c r="C103" t="str">
-        <v>saxophone, flute, arranging, producing, clarinet, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D103" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3131,10 +3836,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>flyin-overhead-single</v>
+        <v>san-fermin</v>
       </c>
       <c r="B104" t="str">
-        <v>Flyin' Overhead (single)</v>
+        <v>Sonsick</v>
       </c>
       <c r="C104" t="str">
         <v>saxophone</v>
@@ -3145,10 +3850,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>presentable-corpse-002</v>
+        <v>san-fermin</v>
       </c>
       <c r="B105" t="str">
-        <v>Blocking Out the Horror</v>
+        <v>Methuselah</v>
       </c>
       <c r="C105" t="str">
         <v>saxophone</v>
@@ -3159,10 +3864,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>varsovia-single</v>
+        <v>san-fermin</v>
       </c>
       <c r="B106" t="str">
-        <v>Varsovia (Single)</v>
+        <v>At Sea</v>
       </c>
       <c r="C106" t="str">
         <v>saxophone</v>
@@ -3173,13 +3878,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>asphalt-homeland-single</v>
+        <v>san-fermin</v>
       </c>
       <c r="B107" t="str">
-        <v>Asphalt Homeland (Single)</v>
+        <v>Torero</v>
       </c>
       <c r="C107" t="str">
-        <v>saxophone, flute</v>
+        <v>saxophone</v>
       </c>
       <c r="D107" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3187,13 +3892,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>unknown-caller</v>
+        <v>san-fermin</v>
       </c>
       <c r="B108" t="str">
-        <v>Folded Up</v>
+        <v>At Night, True Love</v>
       </c>
       <c r="C108" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D108" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3201,13 +3906,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>unknown-caller</v>
+        <v>san-fermin</v>
       </c>
       <c r="B109" t="str">
-        <v>How to Be Alone</v>
+        <v>The Count</v>
       </c>
       <c r="C109" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D109" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3215,13 +3920,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>unknown-caller</v>
+        <v>san-fermin</v>
       </c>
       <c r="B110" t="str">
-        <v>June 20th, 1943</v>
+        <v>Bar</v>
       </c>
       <c r="C110" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D110" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3229,13 +3934,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>cassandra-deluxe-edition</v>
+        <v>san-fermin</v>
       </c>
       <c r="B111" t="str">
-        <v>Cassandra</v>
+        <v>In Waiting</v>
       </c>
       <c r="C111" t="str">
-        <v>saxophone, vocals, writing, arranging, producing, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D111" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3243,13 +3948,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>cassandra-deluxe-edition</v>
+        <v>san-fermin</v>
       </c>
       <c r="B112" t="str">
-        <v>Cassandra (instrumental)</v>
+        <v>True Love, Asleep</v>
       </c>
       <c r="C112" t="str">
-        <v>saxophone, vocals, writing, arranging, producing, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D112" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3257,13 +3962,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>xito</v>
+        <v>san-fermin</v>
       </c>
       <c r="B113" t="str">
-        <v>Welcome to the Boogie</v>
+        <v>Oh Darling</v>
       </c>
       <c r="C113" t="str">
-        <v>producing, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D113" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3271,13 +3976,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>xito</v>
+        <v>san-fermin</v>
       </c>
       <c r="B114" t="str">
-        <v>Salvation</v>
+        <v>In The Morning</v>
       </c>
       <c r="C114" t="str">
-        <v>producing, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D114" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3285,13 +3990,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>xito</v>
+        <v>san-fermin</v>
       </c>
       <c r="B115" t="str">
-        <v>En Guayubin No Llueve</v>
+        <v>Daedalus (What We Have)</v>
       </c>
       <c r="C115" t="str">
-        <v>producing, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D115" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3299,13 +4004,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>xito</v>
+        <v>san-fermin</v>
       </c>
       <c r="B116" t="str">
-        <v>Sugar</v>
+        <v>Altogether Changed</v>
       </c>
       <c r="C116" t="str">
-        <v>producing, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D116" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3313,13 +4018,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>xito</v>
+        <v>scattered-air</v>
       </c>
       <c r="B117" t="str">
-        <v>Tu Si Puedes</v>
+        <v>Tuned to Break</v>
       </c>
       <c r="C117" t="str">
-        <v>producing, arranging, saxophone</v>
+        <v>saxophone, writing, arranging, vocals, keyboards</v>
       </c>
       <c r="D117" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3327,13 +4032,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>notes-from-quarantine</v>
+        <v>scattered-air</v>
       </c>
       <c r="B118" t="str">
-        <v>Night Walker (Remix)</v>
+        <v>Fact</v>
       </c>
       <c r="C118" t="str">
-        <v>saxophone, flute</v>
+        <v>saxophone, writing, arranging, vocals, keyboards</v>
       </c>
       <c r="D118" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3341,13 +4046,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>notes-from-quarantine</v>
+        <v>scattered-air</v>
       </c>
       <c r="B119" t="str">
-        <v>Fuzz Salsa</v>
+        <v>Rearview</v>
       </c>
       <c r="C119" t="str">
-        <v>saxophone, flute</v>
+        <v>saxophone, writing, arranging, vocals, keyboards</v>
       </c>
       <c r="D119" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3355,13 +4060,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>scattered-air</v>
       </c>
       <c r="B120" t="str">
-        <v>Introduction</v>
+        <v>Son</v>
       </c>
       <c r="C120" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone, writing, arranging, vocals, keyboards</v>
       </c>
       <c r="D120" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3369,13 +4074,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>varsovia-single</v>
       </c>
       <c r="B121" t="str">
-        <v>Overture</v>
+        <v>Varsovia (Single)</v>
       </c>
       <c r="C121" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D121" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3383,13 +4088,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>bedford-single</v>
       </c>
       <c r="B122" t="str">
-        <v>Little Bird</v>
+        <v>Bedford (Single)</v>
       </c>
       <c r="C122" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D122" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3397,13 +4102,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B123" t="str">
-        <v>Stoop Talk</v>
+        <v>Opening</v>
       </c>
       <c r="C123" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D123" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3411,13 +4116,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B124" t="str">
-        <v>Step Back (Wild Child)</v>
+        <v>Eyes of Love</v>
       </c>
       <c r="C124" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D124" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3425,13 +4130,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B125" t="str">
-        <v>Fuzzy Logic</v>
+        <v>Where To?</v>
       </c>
       <c r="C125" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D125" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3439,13 +4144,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B126" t="str">
-        <v>Pause I</v>
+        <v>To The Moon!</v>
       </c>
       <c r="C126" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D126" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3453,13 +4158,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B127" t="str">
-        <v>Quiet Soul</v>
+        <v>Achluo</v>
       </c>
       <c r="C127" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D127" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3467,13 +4172,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B128" t="str">
-        <v>Mourning</v>
+        <v>Nova</v>
       </c>
       <c r="C128" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D128" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3481,13 +4186,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B129" t="str">
-        <v>Drop Me A Line</v>
+        <v>Helios</v>
       </c>
       <c r="C129" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D129" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3495,13 +4200,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B130" t="str">
-        <v>Pause II</v>
+        <v>Into The Abyss</v>
       </c>
       <c r="C130" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D130" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3509,13 +4214,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B131" t="str">
-        <v>Queen Bee</v>
+        <v>Again</v>
       </c>
       <c r="C131" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D131" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3523,13 +4228,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B132" t="str">
-        <v>Korban Olah</v>
+        <v>A Solar Wind</v>
       </c>
       <c r="C132" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D132" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3537,13 +4242,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B133" t="str">
-        <v>Toujours</v>
+        <v>Space Walk</v>
       </c>
       <c r="C133" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D133" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3551,13 +4256,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B134" t="str">
-        <v>Pause III</v>
+        <v>Casadastra</v>
       </c>
       <c r="C134" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D134" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3565,13 +4270,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B135" t="str">
-        <v>King Of Misdirection</v>
+        <v>A Rare View</v>
       </c>
       <c r="C135" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D135" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3579,13 +4284,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>an-ode-to-escapism</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B136" t="str">
-        <v>Cost Of Living</v>
+        <v>Totality</v>
       </c>
       <c r="C136" t="str">
-        <v>saxophone, clarinet</v>
+        <v>saxophone</v>
       </c>
       <c r="D136" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3593,10 +4298,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>every-feeling-i-ve-ever-felt</v>
+        <v>a-trip-to-the-moon</v>
       </c>
       <c r="B137" t="str">
-        <v>Every Feeling I've Ever Felt</v>
+        <v>Infinite Dark</v>
       </c>
       <c r="C137" t="str">
         <v>saxophone</v>
@@ -3607,13 +4312,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>still-here</v>
+        <v>fuck-la-i-love-la-deluxe-edition</v>
       </c>
       <c r="B138" t="str">
-        <v>I Knew It Was You</v>
+        <v>Fuck LA</v>
       </c>
       <c r="C138" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D138" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3621,13 +4326,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>rain-on-havana</v>
+        <v>fuck-la-i-love-la-deluxe-edition</v>
       </c>
       <c r="B139" t="str">
-        <v>Rain on Havana</v>
+        <v>I Love LA</v>
       </c>
       <c r="C139" t="str">
-        <v>bass</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D139" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3635,13 +4340,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>don-t-forget-single</v>
+        <v>cassandra-deluxe-edition</v>
       </c>
       <c r="B140" t="str">
-        <v>Don't Forget (single)</v>
+        <v>Cassandra</v>
       </c>
       <c r="C140" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D140" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3649,13 +4354,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>jailbird-single</v>
+        <v>cassandra-deluxe-edition</v>
       </c>
       <c r="B141" t="str">
-        <v>Jailbird (Single)</v>
+        <v>Cassandra (instrumental)</v>
       </c>
       <c r="C141" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D141" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3663,13 +4368,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B142" t="str">
-        <v>The Cormorant</v>
+        <v>Introduction</v>
       </c>
       <c r="C142" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D142" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3677,13 +4382,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B143" t="str">
-        <v>Cerulean Gardens</v>
+        <v>Overture</v>
       </c>
       <c r="C143" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D143" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3691,13 +4396,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B144" t="str">
-        <v>Hickman Creek</v>
+        <v>Little Bird</v>
       </c>
       <c r="C144" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D144" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3705,13 +4410,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B145" t="str">
-        <v>The Hunger</v>
+        <v>Stoop Talk</v>
       </c>
       <c r="C145" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D145" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3719,13 +4424,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B146" t="str">
-        <v>Summer by the Void</v>
+        <v>Step Back (Wild Child)</v>
       </c>
       <c r="C146" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D146" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3733,13 +4438,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B147" t="str">
-        <v>Saints</v>
+        <v>Fuzzy Logic</v>
       </c>
       <c r="C147" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D147" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3747,13 +4452,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B148" t="str">
-        <v>The Living</v>
+        <v>Pause I</v>
       </c>
       <c r="C148" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D148" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3761,13 +4466,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B149" t="str">
-        <v>The Myth</v>
+        <v>Quiet Soul</v>
       </c>
       <c r="C149" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D149" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3775,13 +4480,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B150" t="str">
-        <v>Swamp Song</v>
+        <v>Mourning</v>
       </c>
       <c r="C150" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D150" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3789,13 +4494,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B151" t="str">
-        <v>Westfjords</v>
+        <v>Drop Me A Line</v>
       </c>
       <c r="C151" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D151" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3803,13 +4508,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B152" t="str">
-        <v>Do Less</v>
+        <v>Pause II</v>
       </c>
       <c r="C152" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D152" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3817,13 +4522,13 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B153" t="str">
-        <v>Little Star</v>
+        <v>Queen Bee</v>
       </c>
       <c r="C153" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D153" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3831,13 +4536,13 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B154" t="str">
-        <v>Berkley Bridge</v>
+        <v>Korban Olah</v>
       </c>
       <c r="C154" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D154" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3845,13 +4550,13 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B155" t="str">
-        <v>Freedom (Yeah Yeah!)</v>
+        <v>Toujours</v>
       </c>
       <c r="C155" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D155" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3859,13 +4564,13 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B156" t="str">
-        <v>Waterworld</v>
+        <v>Pause III</v>
       </c>
       <c r="C156" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D156" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3873,13 +4578,13 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>the-cormorant-i-ii</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B157" t="str">
-        <v>Tunnel Mt.</v>
+        <v>King Of Misdirection</v>
       </c>
       <c r="C157" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D157" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3887,13 +4592,13 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>an-ode-to-escapism</v>
       </c>
       <c r="B158" t="str">
-        <v>The Woods - Live</v>
+        <v>Cost Of Living</v>
       </c>
       <c r="C158" t="str">
-        <v>saxophone</v>
+        <v>saxophone, clarinet</v>
       </c>
       <c r="D158" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3901,13 +4606,13 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>night-walker-death-waltz</v>
       </c>
       <c r="B159" t="str">
-        <v>Bride - Live</v>
+        <v>Lost Soul</v>
       </c>
       <c r="C159" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone, flute</v>
       </c>
       <c r="D159" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3915,13 +4620,13 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>sharks-single</v>
       </c>
       <c r="B160" t="str">
-        <v>Emily - Live</v>
+        <v>Sharks (single)</v>
       </c>
       <c r="C160" t="str">
-        <v>saxophone</v>
+        <v>saxophone, arranging, writing</v>
       </c>
       <c r="D160" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3929,13 +4634,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>3-songs</v>
       </c>
       <c r="B161" t="str">
-        <v>Open - Live</v>
+        <v>Ohio (feat. Samia)</v>
       </c>
       <c r="C161" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D161" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3943,13 +4648,13 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>3-songs</v>
       </c>
       <c r="B162" t="str">
-        <v>Better Company - Live</v>
+        <v>Leferever</v>
       </c>
       <c r="C162" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D162" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3957,13 +4662,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>3-songs</v>
       </c>
       <c r="B163" t="str">
-        <v>No Promises - Live</v>
+        <v>A Scene From The Eau Gallie Causeway</v>
       </c>
       <c r="C163" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D163" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -3971,10 +4676,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B164" t="str">
-        <v>Methuselah - Live</v>
+        <v>The Wind Was Like A Train</v>
       </c>
       <c r="C164" t="str">
         <v>saxophone</v>
@@ -3985,10 +4690,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B165" t="str">
-        <v>At Sea - Live</v>
+        <v>Bigger Than Christmas</v>
       </c>
       <c r="C165" t="str">
         <v>saxophone</v>
@@ -3999,10 +4704,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B166" t="str">
-        <v>Ladies Mary - Live</v>
+        <v>The Shining But Tropical</v>
       </c>
       <c r="C166" t="str">
         <v>saxophone</v>
@@ -4013,13 +4718,13 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B167" t="str">
-        <v>Oceanica - Live</v>
+        <v>Amalfi</v>
       </c>
       <c r="C167" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D167" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4027,13 +4732,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B168" t="str">
-        <v>Dead - Live</v>
+        <v>Oversharers Anonymous</v>
       </c>
       <c r="C168" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D168" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4041,10 +4746,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B169" t="str">
-        <v>Astronaut - Live</v>
+        <v>You Can Have It Back</v>
       </c>
       <c r="C169" t="str">
         <v>saxophone</v>
@@ -4055,13 +4760,13 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B170" t="str">
-        <v>Cairo - Live</v>
+        <v>Family Friends</v>
       </c>
       <c r="C170" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D170" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4069,13 +4774,13 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B171" t="str">
-        <v>Oh Darling - Live</v>
+        <v>Track Mud</v>
       </c>
       <c r="C171" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D171" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4083,13 +4788,13 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B172" t="str">
-        <v>Asleep on the Train - Live</v>
+        <v>Pacific City</v>
       </c>
       <c r="C172" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D172" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4097,10 +4802,10 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-billion-little-lights</v>
       </c>
       <c r="B173" t="str">
-        <v>Parasites - Live</v>
+        <v>Die Outside</v>
       </c>
       <c r="C173" t="str">
         <v>saxophone</v>
@@ -4111,10 +4816,10 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B174" t="str">
-        <v>Sonsick - Live</v>
+        <v>Introduction</v>
       </c>
       <c r="C174" t="str">
         <v>saxophone</v>
@@ -4125,13 +4830,13 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B175" t="str">
-        <v>Belong - Live</v>
+        <v>Your Man's No Good</v>
       </c>
       <c r="C175" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D175" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4139,10 +4844,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B176" t="str">
-        <v>Palisades/Storm - Live</v>
+        <v>Scatter</v>
       </c>
       <c r="C176" t="str">
         <v>saxophone</v>
@@ -4153,13 +4858,13 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B177" t="str">
-        <v>Happiness Will Ruin This Place - Live</v>
+        <v>Prism</v>
       </c>
       <c r="C177" t="str">
-        <v>saxophone, arranging</v>
+        <v>saxophone</v>
       </c>
       <c r="D177" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4167,10 +4872,10 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B178" t="str">
-        <v>Renaissance - Live</v>
+        <v>Quiet Places</v>
       </c>
       <c r="C178" t="str">
         <v>saxophone</v>
@@ -4181,10 +4886,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>live-at-the-fillmore</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B179" t="str">
-        <v>Jackrabbit - Live</v>
+        <v>A New Kind Of Love (pt. 1)</v>
       </c>
       <c r="C179" t="str">
         <v>saxophone</v>
@@ -4195,10 +4900,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>a-song-for-paul</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B180" t="str">
-        <v>Intro</v>
+        <v>Why?</v>
       </c>
       <c r="C180" t="str">
         <v>saxophone</v>
@@ -4209,10 +4914,10 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>a-song-for-paul</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B181" t="str">
-        <v>Walk Like A Motherfucker</v>
+        <v>Blockhead</v>
       </c>
       <c r="C181" t="str">
         <v>saxophone</v>
@@ -4223,10 +4928,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>a-song-for-paul</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B182" t="str">
-        <v>Kaddish</v>
+        <v>A Song For Pearl</v>
       </c>
       <c r="C182" t="str">
         <v>saxophone</v>
@@ -4237,10 +4942,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>a-song-for-paul</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B183" t="str">
-        <v>Modern Scene</v>
+        <v>Bluebell</v>
       </c>
       <c r="C183" t="str">
         <v>saxophone</v>
@@ -4251,10 +4956,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>a-song-for-paul</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B184" t="str">
-        <v>Slow Down</v>
+        <v>Rooted</v>
       </c>
       <c r="C184" t="str">
         <v>saxophone</v>
@@ -4265,10 +4970,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>a-song-for-paul</v>
+        <v>a-new-kind-of-love</v>
       </c>
       <c r="B185" t="str">
-        <v>Interlude</v>
+        <v>A New Kind Of Love (pt. 2)</v>
       </c>
       <c r="C185" t="str">
         <v>saxophone</v>
@@ -4279,13 +4984,13 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>a-song-for-paul</v>
+        <v>notes-from-quarantine</v>
       </c>
       <c r="B186" t="str">
-        <v>A Song For Paul</v>
+        <v>Night Walker (Remix)</v>
       </c>
       <c r="C186" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute</v>
       </c>
       <c r="D186" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4293,13 +4998,13 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>a-song-for-paul</v>
+        <v>notes-from-quarantine</v>
       </c>
       <c r="B187" t="str">
-        <v>Spirits In The Distance</v>
+        <v>Fuzz Salsa</v>
       </c>
       <c r="C187" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute</v>
       </c>
       <c r="D187" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4310,7 +5015,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B188" t="str">
-        <v>Seven Eight</v>
+        <v>Intro</v>
       </c>
       <c r="C188" t="str">
         <v>saxophone</v>
@@ -4324,7 +5029,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B189" t="str">
-        <v>Broken Boogaloo</v>
+        <v>Walk Like A Motherfucker</v>
       </c>
       <c r="C189" t="str">
         <v>saxophone</v>
@@ -4338,7 +5043,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B190" t="str">
-        <v>Skin I'm In</v>
+        <v>Kaddish</v>
       </c>
       <c r="C190" t="str">
         <v>saxophone</v>
@@ -4352,7 +5057,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B191" t="str">
-        <v>Isaac Hayes</v>
+        <v>Modern Scene</v>
       </c>
       <c r="C191" t="str">
         <v>saxophone</v>
@@ -4366,7 +5071,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B192" t="str">
-        <v>Interlude II</v>
+        <v>Slow Down</v>
       </c>
       <c r="C192" t="str">
         <v>saxophone</v>
@@ -4380,7 +5085,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B193" t="str">
-        <v>A Conversation</v>
+        <v>Interlude</v>
       </c>
       <c r="C193" t="str">
         <v>saxophone</v>
@@ -4394,7 +5099,7 @@
         <v>a-song-for-paul</v>
       </c>
       <c r="B194" t="str">
-        <v>Outro</v>
+        <v>A Song For Paul</v>
       </c>
       <c r="C194" t="str">
         <v>saxophone</v>
@@ -4405,13 +5110,13 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B195" t="str">
-        <v>Dirty Pictures</v>
+        <v>Spirits In The Distance</v>
       </c>
       <c r="C195" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D195" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4419,13 +5124,13 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B196" t="str">
-        <v>Long Division</v>
+        <v>Seven Eight</v>
       </c>
       <c r="C196" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D196" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4433,13 +5138,13 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B197" t="str">
-        <v>Buddies</v>
+        <v>Broken Boogaloo</v>
       </c>
       <c r="C197" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D197" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4447,13 +5152,13 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B198" t="str">
-        <v>Hard to Please</v>
+        <v>Skin I'm In</v>
       </c>
       <c r="C198" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D198" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4461,13 +5166,13 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B199" t="str">
-        <v>Go Down Fighting</v>
+        <v>Isaac Hayes</v>
       </c>
       <c r="C199" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D199" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4475,13 +5180,13 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B200" t="str">
-        <v>Reptilian</v>
+        <v>Interlude II</v>
       </c>
       <c r="C200" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D200" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4489,13 +5194,13 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>behaviorist-ep</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B201" t="str">
-        <v>Good Guy</v>
+        <v>A Conversation</v>
       </c>
       <c r="C201" t="str">
-        <v>saxophone, vocals, arranging, writing, keyboards, producing</v>
+        <v>saxophone</v>
       </c>
       <c r="D201" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4503,10 +5208,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>pretty-colors-for-your-actions</v>
+        <v>a-song-for-paul</v>
       </c>
       <c r="B202" t="str">
-        <v>House on Fire</v>
+        <v>Outro</v>
       </c>
       <c r="C202" t="str">
         <v>saxophone</v>
@@ -4517,13 +5222,13 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>pretty-colors-for-your-actions</v>
+        <v>a-very-well-balanced-portfolio</v>
       </c>
       <c r="B203" t="str">
-        <v>White Frost</v>
+        <v>The Hits Keep Coming</v>
       </c>
       <c r="C203" t="str">
-        <v>saxophone</v>
+        <v>vocals, drums, writing</v>
       </c>
       <c r="D203" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4531,13 +5236,13 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>pretty-colors-for-your-actions</v>
+        <v>a-very-well-balanced-portfolio</v>
       </c>
       <c r="B204" t="str">
-        <v>Over Now</v>
+        <v>Wasted</v>
       </c>
       <c r="C204" t="str">
-        <v>saxophone</v>
+        <v>vocals, drums, writing</v>
       </c>
       <c r="D204" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4548,10 +5253,10 @@
         <v>a-very-well-balanced-portfolio</v>
       </c>
       <c r="B205" t="str">
-        <v>The Hits Keep Coming</v>
+        <v>Rock Show</v>
       </c>
       <c r="C205" t="str">
-        <v>drums, vocals, writing</v>
+        <v>vocals, drums, writing</v>
       </c>
       <c r="D205" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4562,10 +5267,10 @@
         <v>a-very-well-balanced-portfolio</v>
       </c>
       <c r="B206" t="str">
-        <v>Wasted</v>
+        <v>Jesus Has a Big Dick</v>
       </c>
       <c r="C206" t="str">
-        <v>drums, vocals, writing</v>
+        <v>vocals, drums, writing</v>
       </c>
       <c r="D206" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4573,13 +5278,13 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>a-very-well-balanced-portfolio</v>
+        <v>great-caesar-ep</v>
       </c>
       <c r="B207" t="str">
-        <v>Rock Show</v>
+        <v>Still Love</v>
       </c>
       <c r="C207" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone, vocals, arranging, writing</v>
       </c>
       <c r="D207" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4587,13 +5292,13 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>a-very-well-balanced-portfolio</v>
+        <v>great-caesar-ep</v>
       </c>
       <c r="B208" t="str">
-        <v>Jesus Has a Big Dick</v>
+        <v>Don't Ask Me Why</v>
       </c>
       <c r="C208" t="str">
-        <v>drums, vocals, writing</v>
+        <v>saxophone, vocals, arranging, writing</v>
       </c>
       <c r="D208" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4601,13 +5306,13 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>belong</v>
+        <v>great-caesar-ep</v>
       </c>
       <c r="B209" t="str">
-        <v>Open</v>
+        <v>Holiday</v>
       </c>
       <c r="C209" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, arranging, writing</v>
       </c>
       <c r="D209" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4615,13 +5320,13 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>belong</v>
+        <v>great-caesar-ep</v>
       </c>
       <c r="B210" t="str">
-        <v>Bride</v>
+        <v>Bury Me</v>
       </c>
       <c r="C210" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, arranging, writing</v>
       </c>
       <c r="D210" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4629,10 +5334,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B211" t="str">
-        <v>Oceanica</v>
+        <v>The Woods</v>
       </c>
       <c r="C211" t="str">
         <v>saxophone</v>
@@ -4643,10 +5348,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B212" t="str">
-        <v>August</v>
+        <v>Ladies Mary</v>
       </c>
       <c r="C212" t="str">
         <v>saxophone</v>
@@ -4657,10 +5362,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B213" t="str">
-        <v>Better Company</v>
+        <v>Emily</v>
       </c>
       <c r="C213" t="str">
         <v>saxophone</v>
@@ -4671,10 +5376,10 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B214" t="str">
-        <v>No Promises</v>
+        <v>Jackrabbit</v>
       </c>
       <c r="C214" t="str">
         <v>saxophone</v>
@@ -4685,10 +5390,10 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B215" t="str">
-        <v>Belong</v>
+        <v>Astronaut</v>
       </c>
       <c r="C215" t="str">
         <v>saxophone</v>
@@ -4699,10 +5404,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B216" t="str">
-        <v>Bones</v>
+        <v>Philosopher</v>
       </c>
       <c r="C216" t="str">
         <v>saxophone</v>
@@ -4713,10 +5418,10 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B217" t="str">
-        <v>Dead</v>
+        <v>Ecstatic Thoughts</v>
       </c>
       <c r="C217" t="str">
         <v>saxophone</v>
@@ -4727,10 +5432,10 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B218" t="str">
-        <v>Perfume</v>
+        <v>Woman In Red</v>
       </c>
       <c r="C218" t="str">
         <v>saxophone</v>
@@ -4741,10 +5446,10 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B219" t="str">
-        <v>Cairo</v>
+        <v>The Cave</v>
       </c>
       <c r="C219" t="str">
         <v>saxophone</v>
@@ -4755,10 +5460,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B220" t="str">
-        <v>Palisades/Storm</v>
+        <v>Parasites</v>
       </c>
       <c r="C220" t="str">
         <v>saxophone</v>
@@ -4769,10 +5474,10 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>belong</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B221" t="str">
-        <v>Happiness Will Ruin This Place</v>
+        <v>Reckoning</v>
       </c>
       <c r="C221" t="str">
         <v>saxophone</v>
@@ -4783,13 +5488,13 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>jackson-s-big-sky</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B222" t="str">
-        <v>Hey Mama</v>
+        <v>The Glory</v>
       </c>
       <c r="C222" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone</v>
       </c>
       <c r="D222" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4797,13 +5502,13 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>jackson-s-big-sky</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B223" t="str">
-        <v>Leaving You</v>
+        <v>Two Scenes</v>
       </c>
       <c r="C223" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone</v>
       </c>
       <c r="D223" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4811,13 +5516,13 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jackson-s-big-sky</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B224" t="str">
-        <v>Let Me In</v>
+        <v>Halcyon Days</v>
       </c>
       <c r="C224" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone</v>
       </c>
       <c r="D224" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4825,13 +5530,13 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>jackson-s-big-sky</v>
+        <v>jackrabbit</v>
       </c>
       <c r="B225" t="str">
-        <v>Jolene</v>
+        <v>Billy Bibbit</v>
       </c>
       <c r="C225" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone</v>
       </c>
       <c r="D225" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4839,13 +5544,13 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>night-walker-death-waltz</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B226" t="str">
-        <v>Lost Soul</v>
+        <v>Dirty Pictures</v>
       </c>
       <c r="C226" t="str">
-        <v>saxophone, flute</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D226" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4853,13 +5558,13 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>where-do-you-go-single</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B227" t="str">
-        <v>Where Do You Go (Single)</v>
+        <v>Long Division</v>
       </c>
       <c r="C227" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D227" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4867,13 +5572,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>jackrabbit</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B228" t="str">
-        <v>The Woods</v>
+        <v>Buddies</v>
       </c>
       <c r="C228" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D228" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4881,13 +5586,13 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>jackrabbit</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B229" t="str">
-        <v>Ladies Mary</v>
+        <v>Hard to Please</v>
       </c>
       <c r="C229" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D229" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4895,13 +5600,13 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>jackrabbit</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B230" t="str">
-        <v>Emily</v>
+        <v>Go Down Fighting</v>
       </c>
       <c r="C230" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D230" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4909,13 +5614,13 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>jackrabbit</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B231" t="str">
-        <v>Jackrabbit</v>
+        <v>Reptilian</v>
       </c>
       <c r="C231" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D231" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4923,13 +5628,13 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>jackrabbit</v>
+        <v>behaviorist-ep</v>
       </c>
       <c r="B232" t="str">
-        <v>Astronaut</v>
+        <v>Good Guy</v>
       </c>
       <c r="C232" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, keyboards, arranging, producing, writing</v>
       </c>
       <c r="D232" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -4937,69 +5642,69 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>jackrabbit</v>
+        <v>extra-nice</v>
       </c>
       <c r="B233" t="str">
-        <v>Philosopher</v>
+        <v>Sandwich Kid</v>
       </c>
       <c r="C233" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, clarinet, bass, arranging, engineering, mixing, producing, writing</v>
       </c>
       <c r="D233" t="str">
-        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+        <v/>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>jackrabbit</v>
+        <v>extra-nice</v>
       </c>
       <c r="B234" t="str">
-        <v>Ecstatic Thoughts</v>
+        <v>Open Fields</v>
       </c>
       <c r="C234" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, clarinet, bass, arranging, engineering, mixing, producing, writing</v>
       </c>
       <c r="D234" t="str">
-        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+        <v/>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>jackrabbit</v>
+        <v>extra-nice</v>
       </c>
       <c r="B235" t="str">
-        <v>Woman In Red</v>
+        <v>Small World</v>
       </c>
       <c r="C235" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, clarinet, bass, arranging, engineering, mixing, producing, writing</v>
       </c>
       <c r="D235" t="str">
-        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+        <v/>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>jackrabbit</v>
+        <v>extra-nice</v>
       </c>
       <c r="B236" t="str">
-        <v>The Cave</v>
+        <v>Time Robbers</v>
       </c>
       <c r="C236" t="str">
-        <v>saxophone</v>
+        <v>saxophone, vocals, clarinet, bass, arranging, engineering, mixing, producing, writing</v>
       </c>
       <c r="D236" t="str">
-        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+        <v/>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>jackrabbit</v>
+        <v>bugs</v>
       </c>
       <c r="B237" t="str">
-        <v>Parasites</v>
+        <v>Callous</v>
       </c>
       <c r="C237" t="str">
-        <v>saxophone</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D237" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5007,13 +5712,13 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>jackrabbit</v>
+        <v>bugs</v>
       </c>
       <c r="B238" t="str">
-        <v>Reckoning</v>
+        <v>Stay</v>
       </c>
       <c r="C238" t="str">
-        <v>saxophone</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D238" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5021,13 +5726,13 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>jackrabbit</v>
+        <v>bugs</v>
       </c>
       <c r="B239" t="str">
-        <v>The Glory</v>
+        <v>Scatter</v>
       </c>
       <c r="C239" t="str">
-        <v>saxophone</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D239" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5035,13 +5740,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>jackrabbit</v>
+        <v>bugs</v>
       </c>
       <c r="B240" t="str">
-        <v>Two Scenes</v>
+        <v>Here to Stay</v>
       </c>
       <c r="C240" t="str">
-        <v>saxophone</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D240" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5049,13 +5754,13 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>jackrabbit</v>
+        <v>bugs</v>
       </c>
       <c r="B241" t="str">
-        <v>Halcyon Days</v>
+        <v>Grow Old</v>
       </c>
       <c r="C241" t="str">
-        <v>saxophone</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D241" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5063,13 +5768,13 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>jackrabbit</v>
+        <v>bugs</v>
       </c>
       <c r="B242" t="str">
-        <v>Billy Bibbit</v>
+        <v>Inimitable</v>
       </c>
       <c r="C242" t="str">
-        <v>saxophone</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D242" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5077,13 +5782,13 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>sharks-single</v>
+        <v>bugs</v>
       </c>
       <c r="B243" t="str">
-        <v>Sharks (single)</v>
+        <v>Intention</v>
       </c>
       <c r="C243" t="str">
-        <v>saxophone, writing, arranging</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D243" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5091,13 +5796,13 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>great-caesar-ep</v>
+        <v>bugs</v>
       </c>
       <c r="B244" t="str">
-        <v>Still Love</v>
+        <v>Lighter Shouldered</v>
       </c>
       <c r="C244" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D244" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5105,13 +5810,13 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>great-caesar-ep</v>
+        <v>bugs</v>
       </c>
       <c r="B245" t="str">
-        <v>Don't Ask Me Why</v>
+        <v>Typical</v>
       </c>
       <c r="C245" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D245" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5119,13 +5824,13 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>great-caesar-ep</v>
+        <v>bugs</v>
       </c>
       <c r="B246" t="str">
-        <v>Holiday</v>
+        <v>Lilac</v>
       </c>
       <c r="C246" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone, keyboards, arranging, engineering, producing</v>
       </c>
       <c r="D246" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5133,13 +5838,13 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>great-caesar-ep</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B247" t="str">
-        <v>Bury Me</v>
+        <v>County Road 458</v>
       </c>
       <c r="C247" t="str">
-        <v>saxophone, writing, arranging, vocals</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D247" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5147,13 +5852,13 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>san-fermin</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B248" t="str">
-        <v>Renaissance!</v>
+        <v>Goodbye</v>
       </c>
       <c r="C248" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D248" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5161,13 +5866,13 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>san-fermin</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B249" t="str">
-        <v>Crueler Kind</v>
+        <v>Julia</v>
       </c>
       <c r="C249" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D249" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5175,13 +5880,13 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>san-fermin</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B250" t="str">
-        <v>Lament For V.G.</v>
+        <v>Diamond Ring</v>
       </c>
       <c r="C250" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D250" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5189,13 +5894,13 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>san-fermin</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B251" t="str">
-        <v>Casanova</v>
+        <v>Heart Like Thunder</v>
       </c>
       <c r="C251" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D251" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5203,13 +5908,13 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>san-fermin</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B252" t="str">
-        <v>Sonsick</v>
+        <v>Geraldine</v>
       </c>
       <c r="C252" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D252" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5217,13 +5922,13 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>san-fermin</v>
+        <v>heart-like-thunder</v>
       </c>
       <c r="B253" t="str">
-        <v>Methuselah</v>
+        <v>Shenandoah</v>
       </c>
       <c r="C253" t="str">
-        <v>saxophone</v>
+        <v>saxophone, flute, clarinet, arranging, engineering, producing</v>
       </c>
       <c r="D253" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5231,10 +5936,10 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B254" t="str">
-        <v>At Sea</v>
+        <v>Weird Environment</v>
       </c>
       <c r="C254" t="str">
         <v>saxophone</v>
@@ -5245,10 +5950,10 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B255" t="str">
-        <v>Torero</v>
+        <v>Didn't Want You To</v>
       </c>
       <c r="C255" t="str">
         <v>saxophone</v>
@@ -5259,10 +5964,10 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B256" t="str">
-        <v>At Night, True Love</v>
+        <v>Can't Unsee It</v>
       </c>
       <c r="C256" t="str">
         <v>saxophone</v>
@@ -5273,10 +5978,10 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B257" t="str">
-        <v>The Count</v>
+        <v>Arms</v>
       </c>
       <c r="C257" t="str">
         <v>saxophone</v>
@@ -5287,10 +5992,10 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B258" t="str">
-        <v>Bar</v>
+        <v>Makes Me Want You</v>
       </c>
       <c r="C258" t="str">
         <v>saxophone</v>
@@ -5301,10 +6006,10 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B259" t="str">
-        <v>In Waiting</v>
+        <v>My Love is a Loneliness</v>
       </c>
       <c r="C259" t="str">
         <v>saxophone</v>
@@ -5315,10 +6020,10 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B260" t="str">
-        <v>True Love, Asleep</v>
+        <v>Useful Lies</v>
       </c>
       <c r="C260" t="str">
         <v>saxophone</v>
@@ -5329,10 +6034,10 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B261" t="str">
-        <v>Oh Darling</v>
+        <v>Wasting on Me</v>
       </c>
       <c r="C261" t="str">
         <v>saxophone</v>
@@ -5343,10 +6048,10 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>san-fermin</v>
+        <v>arms</v>
       </c>
       <c r="B262" t="str">
-        <v>In The Morning</v>
+        <v>You Owe Me</v>
       </c>
       <c r="C262" t="str">
         <v>saxophone</v>
@@ -5357,13 +6062,13 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>san-fermin</v>
+        <v>jackson-s-big-sky</v>
       </c>
       <c r="B263" t="str">
-        <v>Daedalus (What We Have)</v>
+        <v>Hey Mama</v>
       </c>
       <c r="C263" t="str">
-        <v>saxophone</v>
+        <v>saxophone, writing, arranging, vocals</v>
       </c>
       <c r="D263" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5371,13 +6076,13 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>san-fermin</v>
+        <v>jackson-s-big-sky</v>
       </c>
       <c r="B264" t="str">
-        <v>Altogether Changed</v>
+        <v>Leaving You</v>
       </c>
       <c r="C264" t="str">
-        <v>saxophone</v>
+        <v>saxophone, writing, arranging, vocals</v>
       </c>
       <c r="D264" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5385,13 +6090,13 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>scattered-air</v>
+        <v>jackson-s-big-sky</v>
       </c>
       <c r="B265" t="str">
-        <v>Tuned to Break</v>
+        <v>Let Me In</v>
       </c>
       <c r="C265" t="str">
-        <v>saxophone, writing, arranging, vocals, keyboards</v>
+        <v>saxophone, writing, arranging, vocals</v>
       </c>
       <c r="D265" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5399,13 +6104,13 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>scattered-air</v>
+        <v>jackson-s-big-sky</v>
       </c>
       <c r="B266" t="str">
-        <v>Fact</v>
+        <v>Jolene</v>
       </c>
       <c r="C266" t="str">
-        <v>saxophone, writing, arranging, vocals, keyboards</v>
+        <v>saxophone, writing, arranging, vocals</v>
       </c>
       <c r="D266" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5413,13 +6118,13 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>scattered-air</v>
+        <v>asphalt-homeland-single</v>
       </c>
       <c r="B267" t="str">
-        <v>Rearview</v>
+        <v>Asphalt Homeland (Single)</v>
       </c>
       <c r="C267" t="str">
-        <v>saxophone, writing, arranging, vocals, keyboards</v>
+        <v>saxophone, flute</v>
       </c>
       <c r="D267" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
@@ -5427,21 +6132,396 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>scattered-air</v>
+        <v>jailbird-single</v>
       </c>
       <c r="B268" t="str">
-        <v>Son</v>
+        <v>Jailbird (Single)</v>
       </c>
       <c r="C268" t="str">
-        <v>saxophone, writing, arranging, vocals, keyboards</v>
+        <v>saxophone</v>
       </c>
       <c r="D268" t="str">
+        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>presentable-corpse-002</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Blocking Out the Horror</v>
+      </c>
+      <c r="C269" t="str">
+        <v>saxophone</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>pretty-colors-for-your-actions</v>
+      </c>
+      <c r="B270" t="str">
+        <v>House on Fire</v>
+      </c>
+      <c r="C270" t="str">
+        <v/>
+      </c>
+      <c r="D270" t="str">
+        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>pretty-colors-for-your-actions</v>
+      </c>
+      <c r="B271" t="str">
+        <v>White Frost</v>
+      </c>
+      <c r="C271" t="str">
+        <v/>
+      </c>
+      <c r="D271" t="str">
+        <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>pretty-colors-for-your-actions</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Over Now</v>
+      </c>
+      <c r="C272" t="str">
+        <v/>
+      </c>
+      <c r="D272" t="str">
         <v>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum. Curabitur pretium tincidunt lacus, at velit vehicula viverra. Sed ac dolor sit amet purus malesuada congue. Nulla facilisi. Praesent ac magna sit amet nunc tristique euismod.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D268"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D272"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D22"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>artist</v>
+      </c>
+      <c r="B1" t="str">
+        <v>website</v>
+      </c>
+      <c r="C1" t="str">
+        <v>instagram</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tiktok</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Behaviorist</v>
+      </c>
+      <c r="B2" t="str">
+        <v>https://behavioristmusic.com</v>
+      </c>
+      <c r="C2" t="str">
+        <v>https://instagram.com/behavioristmusic</v>
+      </c>
+      <c r="D2" t="str">
+        <v>https://www.tiktok.com/@behavioristmusic</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Charlotte Day Wilson</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Communist Daughter</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Ellen Winter</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Extra Nice</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>https://instagram.com/extranicemusic</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Ghost Funk Orchestra</v>
+      </c>
+      <c r="B7" t="str">
+        <v>https://ghostfunkorchestra.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://instagram.com/ghostfunkorchestra</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Great Caesar</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>https://instagram.com/greatcaesarband</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Hallie Spoor</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>https://instagram.com/halliespoormusic</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Jae Shin</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>https://instagram.com/majaeshin</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Jorge Elbrecht</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>https://instagram.com/jorge_elbrecht</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Keren Abreu</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>San Fermin</v>
+      </c>
+      <c r="B13" t="str">
+        <v>https://sanferminband.com</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://instagram.com/sanferminband</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Scam Avenue</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>https://instagram.com/scamavenue</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Sky Ferreira</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Tall Heights</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>https://instagram.com/tallheights</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Tom West</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>V Spehar</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Ve.Nika</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Wild Pink</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>https://instagram.com/wildpinknyc</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>World's Greatest Detective</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>stereotrash</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>https://instagram.com/stereotrashs</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
   </ignoredErrors>
 </worksheet>
 </file>